--- a/SGC-CKN/Excel/149bebac-d14c-4bc3-9e3f-fc26cc84a077_Cọc_số_PR_-_159_P1_-_139_D800_25-03-2026.xlsx
+++ b/SGC-CKN/Excel/149bebac-d14c-4bc3-9e3f-fc26cc84a077_Cọc_số_PR_-_159_P1_-_139_D800_25-03-2026.xlsx
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>01:45 25/03/2026</t>
+    <t>01:15 25/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -175,7 +175,7 @@
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">01:45
+    <t xml:space="preserve">01:15
 25/03/2026</t>
   </si>
   <si>
@@ -1183,16 +1183,16 @@
         <v>1.75</v>
       </c>
       <c r="G12" s="9">
-        <v>9.85</v>
+        <v>4.85</v>
       </c>
       <c r="H12" s="9">
         <v>0.58</v>
       </c>
       <c r="I12" s="9">
-        <v>8.1</v>
+        <v>3.1</v>
       </c>
       <c r="J12" s="12">
-        <v>13.89</v>
+        <v>5.31</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1215,19 +1215,19 @@
         <v>36</v>
       </c>
       <c r="F13" s="13">
-        <v>9.85</v>
+        <v>4.85</v>
       </c>
       <c r="G13" s="13">
-        <v>18.15</v>
+        <v>8.15</v>
       </c>
       <c r="H13" s="13">
         <v>0.58</v>
       </c>
       <c r="I13" s="13">
-        <v>8.3</v>
+        <v>3.3</v>
       </c>
       <c r="J13" s="12">
-        <v>14.23</v>
+        <v>5.66</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>30</v>
@@ -1250,19 +1250,19 @@
         <v>39</v>
       </c>
       <c r="F14" s="16">
-        <v>18.15</v>
+        <v>8.15</v>
       </c>
       <c r="G14" s="16">
-        <v>26.15</v>
+        <v>16.95</v>
       </c>
       <c r="H14" s="16">
         <v>1.33</v>
       </c>
       <c r="I14" s="16">
-        <v>8</v>
+        <v>8.8</v>
       </c>
       <c r="J14" s="12">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1285,19 +1285,19 @@
         <v>42</v>
       </c>
       <c r="F15" s="19">
-        <v>26.15</v>
+        <v>16.95</v>
       </c>
       <c r="G15" s="19">
-        <v>32.45</v>
+        <v>22.15</v>
       </c>
       <c r="H15" s="19">
         <v>2.58</v>
       </c>
       <c r="I15" s="19">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="J15" s="8">
-        <v>2.44</v>
+        <v>2.01</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1320,19 +1320,19 @@
         <v>45</v>
       </c>
       <c r="F16" s="22">
-        <v>32.45</v>
+        <v>22.15</v>
       </c>
       <c r="G16" s="22">
-        <v>36.15</v>
+        <v>26.15</v>
       </c>
       <c r="H16" s="22">
         <v>0.83</v>
       </c>
       <c r="I16" s="22">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="J16" s="8">
-        <v>4.44</v>
+        <v>4.8</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1355,19 +1355,19 @@
         <v>48</v>
       </c>
       <c r="F17" s="25">
-        <v>36.15</v>
+        <v>26.15</v>
       </c>
       <c r="G17" s="25">
-        <v>40.25</v>
+        <v>34.5</v>
       </c>
       <c r="H17" s="25">
         <v>1.5</v>
       </c>
       <c r="I17" s="25">
-        <v>4.1</v>
-      </c>
-      <c r="J17" s="8">
-        <v>2.73</v>
+        <v>8.35</v>
+      </c>
+      <c r="J17" s="12">
+        <v>5.57</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1390,19 +1390,19 @@
         <v>51</v>
       </c>
       <c r="F18" s="28">
-        <v>40.25</v>
+        <v>34.5</v>
       </c>
       <c r="G18" s="28">
-        <v>44.25</v>
+        <v>44.23</v>
       </c>
       <c r="H18" s="28">
-        <v>2.58</v>
+        <v>2.08</v>
       </c>
       <c r="I18" s="28">
-        <v>4</v>
+        <v>9.73</v>
       </c>
       <c r="J18" s="8">
-        <v>1.55</v>
+        <v>4.67</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1589,16 +1589,16 @@
         <v>1.75</v>
       </c>
       <c r="F3" s="9">
-        <v>9.85</v>
+        <v>4.85</v>
       </c>
       <c r="G3" s="9">
         <v>0.58</v>
       </c>
       <c r="H3" s="9">
-        <v>8.1</v>
+        <v>3.1</v>
       </c>
       <c r="I3" s="12">
-        <v>13.89</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1615,19 +1615,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="13">
-        <v>9.85</v>
+        <v>4.85</v>
       </c>
       <c r="F4" s="13">
-        <v>18.15</v>
+        <v>8.15</v>
       </c>
       <c r="G4" s="13">
         <v>0.58</v>
       </c>
       <c r="H4" s="13">
-        <v>8.3</v>
+        <v>3.3</v>
       </c>
       <c r="I4" s="12">
-        <v>14.23</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1644,19 +1644,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>18.15</v>
+        <v>8.15</v>
       </c>
       <c r="F5" s="16">
-        <v>26.15</v>
+        <v>16.95</v>
       </c>
       <c r="G5" s="16">
         <v>1.33</v>
       </c>
       <c r="H5" s="16">
-        <v>8</v>
+        <v>8.8</v>
       </c>
       <c r="I5" s="12">
-        <v>6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1673,19 +1673,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>26.15</v>
+        <v>16.95</v>
       </c>
       <c r="F6" s="19">
-        <v>32.45</v>
+        <v>22.15</v>
       </c>
       <c r="G6" s="19">
         <v>2.58</v>
       </c>
       <c r="H6" s="19">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="I6" s="8">
-        <v>2.44</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1702,19 +1702,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>32.45</v>
+        <v>22.15</v>
       </c>
       <c r="F7" s="22">
-        <v>36.15</v>
+        <v>26.15</v>
       </c>
       <c r="G7" s="22">
         <v>0.83</v>
       </c>
       <c r="H7" s="22">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I7" s="8">
-        <v>4.44</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1731,19 +1731,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>36.15</v>
+        <v>26.15</v>
       </c>
       <c r="F8" s="25">
-        <v>40.25</v>
+        <v>34.5</v>
       </c>
       <c r="G8" s="25">
         <v>1.5</v>
       </c>
       <c r="H8" s="25">
-        <v>4.1</v>
-      </c>
-      <c r="I8" s="8">
-        <v>2.73</v>
+        <v>8.35</v>
+      </c>
+      <c r="I8" s="12">
+        <v>5.57</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1760,19 +1760,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>40.25</v>
+        <v>34.5</v>
       </c>
       <c r="F9" s="28">
-        <v>44.25</v>
+        <v>44.23</v>
       </c>
       <c r="G9" s="28">
-        <v>2.58</v>
+        <v>2.08</v>
       </c>
       <c r="H9" s="28">
-        <v>4</v>
+        <v>9.73</v>
       </c>
       <c r="I9" s="8">
-        <v>1.55</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1792,16 +1792,16 @@
         <v>0</v>
       </c>
       <c r="F10" s="33">
-        <v>44.25</v>
+        <v>44.23</v>
       </c>
       <c r="G10" s="33">
-        <v>10.42</v>
+        <v>9.92</v>
       </c>
       <c r="H10" s="33">
-        <v>44.25</v>
+        <v>44.23</v>
       </c>
       <c r="I10" s="33">
-        <v>4.25</v>
+        <v>4.46</v>
       </c>
     </row>
   </sheetData>
